--- a/artfynd/A 61558-2025 artfynd.xlsx
+++ b/artfynd/A 61558-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130016741</v>
       </c>
       <c r="B3" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61558-2025 artfynd.xlsx
+++ b/artfynd/A 61558-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130016741</v>
       </c>
       <c r="B3" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 61558-2025 artfynd.xlsx
+++ b/artfynd/A 61558-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130016889</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>130016741</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
